--- a/Omset Kategori-2026-04.xlsx
+++ b/Omset Kategori-2026-04.xlsx
@@ -626,11 +626,16 @@
   <cols>
     <col min="1" max="1" width="2.75" customWidth="1"/>
     <col min="2" max="2" width="17.6875" customWidth="1"/>
-    <col min="3" max="13" width="10" customWidth="1"/>
-    <col min="14" max="14" width="11" customWidth="1"/>
-    <col min="15" max="25" width="10" customWidth="1"/>
-    <col min="26" max="27" width="11" customWidth="1"/>
-    <col min="28" max="32" width="10" customWidth="1"/>
+    <col min="3" max="4" width="10" customWidth="1"/>
+    <col min="5" max="6" width="11" customWidth="1"/>
+    <col min="7" max="11" width="10" customWidth="1"/>
+    <col min="12" max="14" width="11" customWidth="1"/>
+    <col min="15" max="15" width="10" customWidth="1"/>
+    <col min="16" max="22" width="11" customWidth="1"/>
+    <col min="23" max="23" width="10" customWidth="1"/>
+    <col min="24" max="28" width="11" customWidth="1"/>
+    <col min="29" max="29" width="10" customWidth="1"/>
+    <col min="30" max="32" width="11" customWidth="1"/>
     <col min="33" max="33" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1088,11 +1093,11 @@
         <v>0</v>
       </c>
       <c r="AF9" s="12">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="AG9" s="13">
         <f>SUM(C9:AF9)</f>
-        <v>0</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
@@ -1112,7 +1117,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="12">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="G10" s="12">
         <v>0</v>
@@ -1130,34 +1135,34 @@
         <v>0</v>
       </c>
       <c r="L10" s="12">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="M10" s="12">
-        <v>0</v>
+        <v>70000</v>
       </c>
       <c r="N10" s="12">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="O10" s="12">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="P10" s="12">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="Q10" s="12">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="R10" s="12">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="S10" s="12">
-        <v>0</v>
+        <v>225000</v>
       </c>
       <c r="T10" s="12">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="U10" s="12">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="V10" s="12">
         <v>0</v>
@@ -1169,32 +1174,32 @@
         <v>0</v>
       </c>
       <c r="Y10" s="12">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="Z10" s="12">
-        <v>0</v>
+        <v>70000</v>
       </c>
       <c r="AA10" s="12">
-        <v>0</v>
+        <v>110000</v>
       </c>
       <c r="AB10" s="12">
         <v>0</v>
       </c>
       <c r="AC10" s="12">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="AD10" s="12">
-        <v>0</v>
+        <v>110000</v>
       </c>
       <c r="AE10" s="12">
-        <v>0</v>
+        <v>105000</v>
       </c>
       <c r="AF10" s="12">
-        <v>0</v>
+        <v>70000</v>
       </c>
       <c r="AG10" s="13">
         <f>SUM(C10:AF10)</f>
-        <v>0</v>
+        <v>1335000</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
@@ -1212,98 +1217,98 @@
         <v>12</v>
       </c>
       <c r="C12" s="12">
-        <v>0</v>
+        <v>180000</v>
       </c>
       <c r="D12" s="12">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="E12" s="12">
-        <v>0</v>
+        <v>510000</v>
       </c>
       <c r="F12" s="12">
-        <v>0</v>
+        <v>210000</v>
       </c>
       <c r="G12" s="12">
-        <v>0</v>
+        <v>330000</v>
       </c>
       <c r="H12" s="12">
-        <v>0</v>
+        <v>180000</v>
       </c>
       <c r="I12" s="12">
-        <v>0</v>
+        <v>180000</v>
       </c>
       <c r="J12" s="12">
-        <v>0</v>
+        <v>210000</v>
       </c>
       <c r="K12" s="12">
-        <v>0</v>
+        <v>180000</v>
       </c>
       <c r="L12" s="12">
-        <v>0</v>
+        <v>450000</v>
       </c>
       <c r="M12" s="12">
-        <v>0</v>
+        <v>360000</v>
       </c>
       <c r="N12" s="12">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="O12" s="12">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="P12" s="12">
-        <v>0</v>
+        <v>570000</v>
       </c>
       <c r="Q12" s="12">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="R12" s="12">
-        <v>0</v>
+        <v>420000</v>
       </c>
       <c r="S12" s="12">
-        <v>0</v>
+        <v>270000</v>
       </c>
       <c r="T12" s="12">
-        <v>0</v>
+        <v>360000</v>
       </c>
       <c r="U12" s="12">
-        <v>0</v>
+        <v>450000</v>
       </c>
       <c r="V12" s="12">
-        <v>0</v>
+        <v>210000</v>
       </c>
       <c r="W12" s="12">
-        <v>0</v>
+        <v>210000</v>
       </c>
       <c r="X12" s="12">
-        <v>0</v>
+        <v>240000</v>
       </c>
       <c r="Y12" s="12">
-        <v>0</v>
+        <v>210000</v>
       </c>
       <c r="Z12" s="12">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="AA12" s="12">
-        <v>0</v>
+        <v>570000</v>
       </c>
       <c r="AB12" s="12">
-        <v>0</v>
+        <v>480000</v>
       </c>
       <c r="AC12" s="12">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="AD12" s="12">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="AE12" s="12">
-        <v>0</v>
+        <v>270000</v>
       </c>
       <c r="AF12" s="12">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="AG12" s="13">
         <f>SUM(C12:AF12)</f>
-        <v>0</v>
+        <v>8820000</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
@@ -1312,98 +1317,98 @@
         <v>13</v>
       </c>
       <c r="C13" s="12">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="D13" s="12">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="E13" s="12">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="F13" s="12">
-        <v>0</v>
+        <v>450000</v>
       </c>
       <c r="G13" s="12">
-        <v>0</v>
+        <v>650000</v>
       </c>
       <c r="H13" s="12">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="I13" s="12">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="J13" s="12">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="K13" s="12">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="L13" s="12">
-        <v>0</v>
+        <v>700000</v>
       </c>
       <c r="M13" s="12">
-        <v>0</v>
+        <v>650000</v>
       </c>
       <c r="N13" s="12">
-        <v>0</v>
+        <v>900000</v>
       </c>
       <c r="O13" s="12">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="P13" s="12">
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="Q13" s="12">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="R13" s="12">
-        <v>0</v>
+        <v>650000</v>
       </c>
       <c r="S13" s="12">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="T13" s="12">
-        <v>0</v>
+        <v>1150000</v>
       </c>
       <c r="U13" s="12">
-        <v>0</v>
+        <v>1050000</v>
       </c>
       <c r="V13" s="12">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="W13" s="12">
-        <v>0</v>
+        <v>450000</v>
       </c>
       <c r="X13" s="12">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="Y13" s="12">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="Z13" s="12">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="AA13" s="12">
-        <v>0</v>
+        <v>1200000</v>
       </c>
       <c r="AB13" s="12">
-        <v>0</v>
+        <v>1350000</v>
       </c>
       <c r="AC13" s="12">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="AD13" s="12">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="AE13" s="12">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="AF13" s="12">
-        <v>0</v>
+        <v>750000</v>
       </c>
       <c r="AG13" s="13">
         <f>SUM(C13:AF13)</f>
-        <v>0</v>
+        <v>15400000</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
@@ -1438,7 +1443,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="12">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="L14" s="12">
         <v>0</v>
@@ -1453,10 +1458,10 @@
         <v>0</v>
       </c>
       <c r="P14" s="12">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="Q14" s="12">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="R14" s="12">
         <v>0</v>
@@ -1486,10 +1491,10 @@
         <v>0</v>
       </c>
       <c r="AA14" s="12">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="AB14" s="12">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="AC14" s="12">
         <v>0</v>
@@ -1498,14 +1503,14 @@
         <v>0</v>
       </c>
       <c r="AE14" s="12">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="AF14" s="12">
         <v>0</v>
       </c>
       <c r="AG14" s="13">
         <f>SUM(C14:AF14)</f>
-        <v>0</v>
+        <v>240000</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
@@ -1519,95 +1524,95 @@
         <v>0</v>
       </c>
       <c r="D15" s="12">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="E15" s="12">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="F15" s="12">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="G15" s="12">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="H15" s="12">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I15" s="12">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="J15" s="12">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="K15" s="12">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="L15" s="12">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="M15" s="12">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="N15" s="12">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="O15" s="12">
         <v>0</v>
       </c>
       <c r="P15" s="12">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="Q15" s="12">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="R15" s="12">
         <v>0</v>
       </c>
       <c r="S15" s="12">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="T15" s="12">
         <v>0</v>
       </c>
       <c r="U15" s="12">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="V15" s="12">
         <v>0</v>
       </c>
       <c r="W15" s="12">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="X15" s="12">
         <v>0</v>
       </c>
       <c r="Y15" s="12">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="Z15" s="12">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="AA15" s="12">
-        <v>0</v>
+        <v>70000</v>
       </c>
       <c r="AB15" s="12">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="AC15" s="12">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AD15" s="12">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="AE15" s="12">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="AF15" s="12">
         <v>0</v>
       </c>
       <c r="AG15" s="13">
         <f>SUM(C15:AF15)</f>
-        <v>0</v>
+        <v>710000</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
@@ -1618,98 +1623,98 @@
         <v>16</v>
       </c>
       <c r="C16" s="12">
-        <v>0</v>
+        <v>277000</v>
       </c>
       <c r="D16" s="12">
-        <v>0</v>
+        <v>690000</v>
       </c>
       <c r="E16" s="12">
-        <v>0</v>
+        <v>1060000</v>
       </c>
       <c r="F16" s="12">
-        <v>0</v>
+        <v>330000</v>
       </c>
       <c r="G16" s="12">
-        <v>0</v>
+        <v>595000</v>
       </c>
       <c r="H16" s="12">
-        <v>0</v>
+        <v>716000</v>
       </c>
       <c r="I16" s="12">
-        <v>0</v>
+        <v>390000</v>
       </c>
       <c r="J16" s="12">
-        <v>0</v>
+        <v>328000</v>
       </c>
       <c r="K16" s="12">
-        <v>0</v>
+        <v>476000</v>
       </c>
       <c r="L16" s="12">
-        <v>0</v>
+        <v>976000</v>
       </c>
       <c r="M16" s="12">
-        <v>0</v>
+        <v>1123000</v>
       </c>
       <c r="N16" s="12">
-        <v>0</v>
+        <v>884000</v>
       </c>
       <c r="O16" s="12">
-        <v>0</v>
+        <v>560000</v>
       </c>
       <c r="P16" s="12">
-        <v>0</v>
+        <v>765000</v>
       </c>
       <c r="Q16" s="12">
-        <v>0</v>
+        <v>705000</v>
       </c>
       <c r="R16" s="12">
-        <v>0</v>
+        <v>919000</v>
       </c>
       <c r="S16" s="12">
-        <v>0</v>
+        <v>916000</v>
       </c>
       <c r="T16" s="12">
-        <v>0</v>
+        <v>1149000</v>
       </c>
       <c r="U16" s="12">
-        <v>0</v>
+        <v>1484000</v>
       </c>
       <c r="V16" s="12">
-        <v>0</v>
+        <v>567000</v>
       </c>
       <c r="W16" s="12">
-        <v>0</v>
+        <v>680000</v>
       </c>
       <c r="X16" s="12">
-        <v>0</v>
+        <v>1309000</v>
       </c>
       <c r="Y16" s="12">
-        <v>0</v>
+        <v>962000</v>
       </c>
       <c r="Z16" s="12">
-        <v>0</v>
+        <v>1249000</v>
       </c>
       <c r="AA16" s="12">
-        <v>0</v>
+        <v>1283000</v>
       </c>
       <c r="AB16" s="12">
-        <v>0</v>
+        <v>937000</v>
       </c>
       <c r="AC16" s="12">
-        <v>0</v>
+        <v>692000</v>
       </c>
       <c r="AD16" s="12">
-        <v>0</v>
+        <v>810000</v>
       </c>
       <c r="AE16" s="12">
-        <v>0</v>
+        <v>1934000</v>
       </c>
       <c r="AF16" s="12">
-        <v>0</v>
+        <v>835000</v>
       </c>
       <c r="AG16" s="13">
         <f>SUM(C16:AF16)</f>
-        <v>0</v>
+        <v>25601000</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
@@ -1720,98 +1725,98 @@
         <v>17</v>
       </c>
       <c r="C17" s="12">
-        <v>0</v>
+        <v>138000</v>
       </c>
       <c r="D17" s="12">
-        <v>0</v>
+        <v>346000</v>
       </c>
       <c r="E17" s="12">
-        <v>0</v>
+        <v>790000</v>
       </c>
       <c r="F17" s="12">
-        <v>0</v>
+        <v>422000</v>
       </c>
       <c r="G17" s="12">
-        <v>0</v>
+        <v>337000</v>
       </c>
       <c r="H17" s="12">
-        <v>0</v>
+        <v>386000</v>
       </c>
       <c r="I17" s="12">
-        <v>0</v>
+        <v>195000</v>
       </c>
       <c r="J17" s="12">
-        <v>0</v>
+        <v>233000</v>
       </c>
       <c r="K17" s="12">
-        <v>0</v>
+        <v>271000</v>
       </c>
       <c r="L17" s="12">
-        <v>0</v>
+        <v>517000</v>
       </c>
       <c r="M17" s="12">
-        <v>0</v>
+        <v>459000</v>
       </c>
       <c r="N17" s="12">
-        <v>0</v>
+        <v>624000</v>
       </c>
       <c r="O17" s="12">
-        <v>0</v>
+        <v>691000</v>
       </c>
       <c r="P17" s="12">
-        <v>0</v>
+        <v>570000</v>
       </c>
       <c r="Q17" s="12">
-        <v>0</v>
+        <v>459000</v>
       </c>
       <c r="R17" s="12">
-        <v>0</v>
+        <v>654000</v>
       </c>
       <c r="S17" s="12">
-        <v>0</v>
+        <v>525000</v>
       </c>
       <c r="T17" s="12">
-        <v>0</v>
+        <v>535000</v>
       </c>
       <c r="U17" s="12">
-        <v>0</v>
+        <v>390000</v>
       </c>
       <c r="V17" s="12">
-        <v>0</v>
+        <v>614000</v>
       </c>
       <c r="W17" s="12">
-        <v>0</v>
+        <v>313000</v>
       </c>
       <c r="X17" s="12">
-        <v>0</v>
+        <v>454000</v>
       </c>
       <c r="Y17" s="12">
-        <v>0</v>
+        <v>392000</v>
       </c>
       <c r="Z17" s="12">
-        <v>0</v>
+        <v>580000</v>
       </c>
       <c r="AA17" s="12">
-        <v>0</v>
+        <v>636000</v>
       </c>
       <c r="AB17" s="12">
-        <v>0</v>
+        <v>613000</v>
       </c>
       <c r="AC17" s="12">
-        <v>0</v>
+        <v>486000</v>
       </c>
       <c r="AD17" s="12">
-        <v>0</v>
+        <v>700000</v>
       </c>
       <c r="AE17" s="12">
-        <v>0</v>
+        <v>636000</v>
       </c>
       <c r="AF17" s="12">
-        <v>0</v>
+        <v>771000</v>
       </c>
       <c r="AG17" s="13">
         <f>SUM(C17:AF17)</f>
-        <v>0</v>
+        <v>14737000</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
@@ -1822,22 +1827,22 @@
         <v>18</v>
       </c>
       <c r="C18" s="12">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="D18" s="12">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="E18" s="12">
-        <v>0</v>
+        <v>630000</v>
       </c>
       <c r="F18" s="12">
-        <v>0</v>
+        <v>125000</v>
       </c>
       <c r="G18" s="12">
-        <v>0</v>
+        <v>140000</v>
       </c>
       <c r="H18" s="12">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="I18" s="12">
         <v>0</v>
@@ -1849,71 +1854,71 @@
         <v>0</v>
       </c>
       <c r="L18" s="12">
-        <v>0</v>
+        <v>240000</v>
       </c>
       <c r="M18" s="12">
-        <v>0</v>
+        <v>265000</v>
       </c>
       <c r="N18" s="12">
-        <v>0</v>
+        <v>480000</v>
       </c>
       <c r="O18" s="12">
-        <v>0</v>
+        <v>220000</v>
       </c>
       <c r="P18" s="12">
-        <v>0</v>
+        <v>710000</v>
       </c>
       <c r="Q18" s="12">
-        <v>0</v>
+        <v>205000</v>
       </c>
       <c r="R18" s="12">
-        <v>0</v>
+        <v>410000</v>
       </c>
       <c r="S18" s="12">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="T18" s="12">
-        <v>0</v>
+        <v>395000</v>
       </c>
       <c r="U18" s="12">
-        <v>0</v>
+        <v>700000</v>
       </c>
       <c r="V18" s="12">
         <v>0</v>
       </c>
       <c r="W18" s="12">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="X18" s="12">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="Y18" s="12">
-        <v>0</v>
+        <v>180000</v>
       </c>
       <c r="Z18" s="12">
-        <v>0</v>
+        <v>395000</v>
       </c>
       <c r="AA18" s="12">
-        <v>0</v>
+        <v>390000</v>
       </c>
       <c r="AB18" s="12">
-        <v>0</v>
+        <v>540000</v>
       </c>
       <c r="AC18" s="12">
-        <v>0</v>
+        <v>265000</v>
       </c>
       <c r="AD18" s="12">
-        <v>0</v>
+        <v>485000</v>
       </c>
       <c r="AE18" s="12">
         <v>0</v>
       </c>
       <c r="AF18" s="12">
-        <v>0</v>
+        <v>125000</v>
       </c>
       <c r="AG18" s="13">
         <f>SUM(C18:AF18)</f>
-        <v>0</v>
+        <v>7570000</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
@@ -1993,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="Z19" s="12">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="AA19" s="12">
         <v>0</v>
@@ -2015,7 +2020,7 @@
       </c>
       <c r="AG19" s="13">
         <f>SUM(C19:AF19)</f>
-        <v>0</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
@@ -2035,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="12">
-        <v>0</v>
+        <v>840000</v>
       </c>
       <c r="G20" s="12">
         <v>0</v>
@@ -2056,7 +2061,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="12">
-        <v>0</v>
+        <v>210000</v>
       </c>
       <c r="N20" s="12">
         <v>0</v>
@@ -2065,7 +2070,7 @@
         <v>0</v>
       </c>
       <c r="P20" s="12">
-        <v>0</v>
+        <v>420000</v>
       </c>
       <c r="Q20" s="12">
         <v>0</v>
@@ -2083,7 +2088,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="12">
-        <v>0</v>
+        <v>420000</v>
       </c>
       <c r="W20" s="12">
         <v>0</v>
@@ -2098,7 +2103,7 @@
         <v>0</v>
       </c>
       <c r="AA20" s="12">
-        <v>0</v>
+        <v>210000</v>
       </c>
       <c r="AB20" s="12">
         <v>0</v>
@@ -2113,11 +2118,11 @@
         <v>0</v>
       </c>
       <c r="AF20" s="12">
-        <v>0</v>
+        <v>210000</v>
       </c>
       <c r="AG20" s="13">
         <f>SUM(C20:AF20)</f>
-        <v>0</v>
+        <v>2310000</v>
       </c>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
@@ -2239,7 +2244,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="12">
-        <v>0</v>
+        <v>240000</v>
       </c>
       <c r="G22" s="12">
         <v>0</v>
@@ -2269,10 +2274,10 @@
         <v>0</v>
       </c>
       <c r="P22" s="12">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="Q22" s="12">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="R22" s="12">
         <v>0</v>
@@ -2308,7 +2313,7 @@
         <v>0</v>
       </c>
       <c r="AC22" s="12">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="AD22" s="12">
         <v>0</v>
@@ -2317,11 +2322,11 @@
         <v>0</v>
       </c>
       <c r="AF22" s="12">
-        <v>0</v>
+        <v>240000</v>
       </c>
       <c r="AG22" s="13">
         <f>SUM(C22:AF22)</f>
-        <v>0</v>
+        <v>840000</v>
       </c>
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.25">
@@ -2332,7 +2337,7 @@
         <v>23</v>
       </c>
       <c r="C23" s="12">
-        <v>0</v>
+        <v>70000</v>
       </c>
       <c r="D23" s="12">
         <v>0</v>
@@ -2341,19 +2346,19 @@
         <v>0</v>
       </c>
       <c r="F23" s="12">
-        <v>0</v>
+        <v>65000</v>
       </c>
       <c r="G23" s="12">
         <v>0</v>
       </c>
       <c r="H23" s="12">
-        <v>0</v>
+        <v>65000</v>
       </c>
       <c r="I23" s="12">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="J23" s="12">
-        <v>0</v>
+        <v>130000</v>
       </c>
       <c r="K23" s="12">
         <v>0</v>
@@ -2365,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="N23" s="12">
-        <v>0</v>
+        <v>325000</v>
       </c>
       <c r="O23" s="12">
-        <v>0</v>
+        <v>65000</v>
       </c>
       <c r="P23" s="12">
         <v>0</v>
@@ -2377,13 +2382,13 @@
         <v>0</v>
       </c>
       <c r="R23" s="12">
-        <v>0</v>
+        <v>65000</v>
       </c>
       <c r="S23" s="12">
         <v>0</v>
       </c>
       <c r="T23" s="12">
-        <v>0</v>
+        <v>125000</v>
       </c>
       <c r="U23" s="12">
         <v>0</v>
@@ -2416,14 +2421,14 @@
         <v>0</v>
       </c>
       <c r="AE23" s="12">
-        <v>0</v>
+        <v>65000</v>
       </c>
       <c r="AF23" s="12">
-        <v>0</v>
+        <v>245000</v>
       </c>
       <c r="AG23" s="13">
         <f>SUM(C23:AF23)</f>
-        <v>0</v>
+        <v>1280000</v>
       </c>
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.25">
@@ -2464,10 +2469,10 @@
         <v>0</v>
       </c>
       <c r="M24" s="12">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="N24" s="12">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="O24" s="12">
         <v>0</v>
@@ -2479,19 +2484,19 @@
         <v>0</v>
       </c>
       <c r="R24" s="12">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="S24" s="12">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="T24" s="12">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="U24" s="12">
         <v>0</v>
       </c>
       <c r="V24" s="12">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="W24" s="12">
         <v>0</v>
@@ -2503,29 +2508,29 @@
         <v>0</v>
       </c>
       <c r="Z24" s="12">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="AA24" s="12">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="AB24" s="12">
         <v>0</v>
       </c>
       <c r="AC24" s="12">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="AD24" s="12">
         <v>0</v>
       </c>
       <c r="AE24" s="12">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="AF24" s="12">
         <v>0</v>
       </c>
       <c r="AG24" s="13">
         <f>SUM(C24:AF24)</f>
-        <v>0</v>
+        <v>1100000</v>
       </c>
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
@@ -2637,127 +2642,127 @@
       <c r="B26" s="3"/>
       <c r="C26" s="14">
         <f>SUM(C6:C25)</f>
-        <v>2750000</v>
+        <v>3645000</v>
       </c>
       <c r="D26" s="15">
         <f>SUM(D6:D25)</f>
-        <v>7677500</v>
+        <v>9243500</v>
       </c>
       <c r="E26" s="15">
         <f>SUM(E6:E25)</f>
-        <v>9500000</v>
+        <v>13105000</v>
       </c>
       <c r="F26" s="15">
         <f>SUM(F6:F25)</f>
-        <v>8150000</v>
+        <v>10882000</v>
       </c>
       <c r="G26" s="15">
         <f>SUM(G6:G25)</f>
-        <v>6600000</v>
+        <v>8682000</v>
       </c>
       <c r="H26" s="15">
         <f>SUM(H6:H25)</f>
-        <v>5120000</v>
+        <v>6792000</v>
       </c>
       <c r="I26" s="15">
         <f>SUM(I6:I25)</f>
-        <v>6322500</v>
+        <v>7392500</v>
       </c>
       <c r="J26" s="15">
         <f>SUM(J6:J25)</f>
-        <v>4050000</v>
+        <v>5131000</v>
       </c>
       <c r="K26" s="15">
         <f>SUM(K6:K25)</f>
-        <v>4830000</v>
+        <v>5862000</v>
       </c>
       <c r="L26" s="15">
         <f>SUM(L6:L25)</f>
-        <v>8645000</v>
+        <v>11623000</v>
       </c>
       <c r="M26" s="15">
         <f>SUM(M6:M25)</f>
-        <v>7080000</v>
+        <v>10347000</v>
       </c>
       <c r="N26" s="15">
         <f>SUM(N6:N25)</f>
-        <v>10180000</v>
+        <v>13863000</v>
       </c>
       <c r="O26" s="15">
         <f>SUM(O6:O25)</f>
-        <v>7230000</v>
+        <v>9506000</v>
       </c>
       <c r="P26" s="15">
         <f>SUM(P6:P25)</f>
-        <v>9229999</v>
+        <v>13274999</v>
       </c>
       <c r="Q26" s="15">
         <f>SUM(Q6:Q25)</f>
-        <v>7780000</v>
+        <v>10079000</v>
       </c>
       <c r="R26" s="15">
         <f>SUM(R6:R25)</f>
-        <v>9225000</v>
+        <v>12618000</v>
       </c>
       <c r="S26" s="15">
         <f>SUM(S6:S25)</f>
-        <v>8680000</v>
+        <v>10971000</v>
       </c>
       <c r="T26" s="15">
         <f>SUM(T6:T25)</f>
-        <v>9900000</v>
+        <v>13739000</v>
       </c>
       <c r="U26" s="15">
         <f>SUM(U6:U25)</f>
-        <v>9680000</v>
+        <v>13864000</v>
       </c>
       <c r="V26" s="15">
         <f>SUM(V6:V25)</f>
-        <v>8750000</v>
+        <v>10911000</v>
       </c>
       <c r="W26" s="15">
         <f>SUM(W6:W25)</f>
-        <v>7867500</v>
+        <v>9640500</v>
       </c>
       <c r="X26" s="15">
         <f>SUM(X6:X25)</f>
-        <v>8850000</v>
+        <v>11343000</v>
       </c>
       <c r="Y26" s="15">
         <f>SUM(Y6:Y25)</f>
-        <v>8717500</v>
+        <v>10721500</v>
       </c>
       <c r="Z26" s="15">
         <f>SUM(Z6:Z25)</f>
-        <v>10850000</v>
+        <v>15884000</v>
       </c>
       <c r="AA26" s="15">
         <f>SUM(AA6:AA25)</f>
-        <v>10400000</v>
+        <v>15159000</v>
       </c>
       <c r="AB26" s="15">
         <f>SUM(AB6:AB25)</f>
-        <v>8300000</v>
+        <v>12305000</v>
       </c>
       <c r="AC26" s="15">
         <f>SUM(AC6:AC25)</f>
-        <v>7725000</v>
+        <v>9898000</v>
       </c>
       <c r="AD26" s="15">
         <f>SUM(AD6:AD25)</f>
-        <v>9340000</v>
+        <v>11995000</v>
       </c>
       <c r="AE26" s="15">
         <f>SUM(AE6:AE25)</f>
-        <v>8780000</v>
+        <v>12310000</v>
       </c>
       <c r="AF26" s="16">
         <f>SUM(AF6:AF25)</f>
-        <v>9920000</v>
+        <v>13586000</v>
       </c>
       <c r="AG26" s="17">
         <f>SUM(AG6:AG25)</f>
-        <v>242129999</v>
+        <v>324372999</v>
       </c>
     </row>
   </sheetData>
